--- a/VerveStacks_ETH_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_ETH_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ETH_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF63111-9770-40FB-BD4F-6607B10C4629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AAF259-DB30-4FCC-85BD-78F361497835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5942,7 +5942,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF1AAD1-21E4-40CA-9A3F-B8918FF82A32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACFF9CE-B916-4196-B137-4ACA626624DF}">
   <dimension ref="B3:I17"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
